--- a/results_cnn_subnetwork_evaluation/competitors_f(AEC,PS)/cnn_evaluation(stress_test)_type-multiplicative_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_cnn_subnetwork_evaluation/competitors_f(AEC,PS)/cnn_evaluation(stress_test)_type-multiplicative_nm_basis-False_nm_modifier-False.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\competitors_f(AEC,PS)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787DFC12-4E27-4858-801C-F75E3E3D0222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nrr_1.0" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,18 @@
     <sheet name="nrr_0.1" sheetId="7" r:id="rId7"/>
     <sheet name="nrr_0.05" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
